--- a/player_brigade.xlsx
+++ b/player_brigade.xlsx
@@ -2716,7 +2716,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>alive</t>
+          <t>heavy</t>
         </is>
       </c>
       <c r="M38" t="n">
@@ -2776,7 +2776,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>alive</t>
+          <t>light</t>
         </is>
       </c>
       <c r="M39" t="n">
@@ -2836,7 +2836,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>alive</t>
+          <t>light</t>
         </is>
       </c>
       <c r="M40" t="n">
@@ -2896,7 +2896,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>alive</t>
+          <t>light</t>
         </is>
       </c>
       <c r="M41" t="n">
@@ -2956,7 +2956,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>alive</t>
+          <t>light</t>
         </is>
       </c>
       <c r="M42" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>alive</t>
+          <t>light</t>
         </is>
       </c>
       <c r="M43" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>alive</t>
+          <t>light</t>
         </is>
       </c>
       <c r="M44" t="n">
@@ -3136,7 +3136,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>alive</t>
+          <t>light</t>
         </is>
       </c>
       <c r="M45" t="n">
@@ -3196,7 +3196,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>alive</t>
+          <t>killed</t>
         </is>
       </c>
       <c r="M46" t="n">
@@ -3256,7 +3256,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>alive</t>
+          <t>light</t>
         </is>
       </c>
       <c r="M47" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>alive</t>
+          <t>light</t>
         </is>
       </c>
       <c r="M50" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>alive</t>
+          <t>light</t>
         </is>
       </c>
       <c r="M51" t="n">
@@ -3616,7 +3616,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>alive</t>
+          <t>light</t>
         </is>
       </c>
       <c r="M53" t="n">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>alive</t>
+          <t>light</t>
         </is>
       </c>
       <c r="M55" t="n">
@@ -3796,7 +3796,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>alive</t>
+          <t>light</t>
         </is>
       </c>
       <c r="M56" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>alive</t>
+          <t>died_from_injury</t>
         </is>
       </c>
       <c r="M57" t="n">
@@ -3976,7 +3976,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>alive</t>
+          <t>light</t>
         </is>
       </c>
       <c r="M59" t="n">
@@ -3984,7 +3984,7 @@
       </c>
       <c r="N59" t="inlineStr"/>
       <c r="O59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P59" t="n">
         <v>0</v>
@@ -4036,7 +4036,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>alive</t>
+          <t>died_from_injury</t>
         </is>
       </c>
       <c r="M60" t="n">
@@ -4096,7 +4096,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>alive</t>
+          <t>light</t>
         </is>
       </c>
       <c r="M61" t="n">
@@ -4156,7 +4156,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>alive</t>
+          <t>killed</t>
         </is>
       </c>
       <c r="M62" t="n">
@@ -4216,7 +4216,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>alive</t>
+          <t>light</t>
         </is>
       </c>
       <c r="M63" t="n">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>alive</t>
+          <t>heavy</t>
         </is>
       </c>
       <c r="M64" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>alive</t>
+          <t>died_from_injury</t>
         </is>
       </c>
       <c r="M65" t="n">
@@ -4456,7 +4456,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>alive</t>
+          <t>light</t>
         </is>
       </c>
       <c r="M67" t="n">
@@ -4516,7 +4516,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>alive</t>
+          <t>light</t>
         </is>
       </c>
       <c r="M68" t="n">
@@ -4576,7 +4576,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>alive</t>
+          <t>light</t>
         </is>
       </c>
       <c r="M69" t="n">
@@ -4636,7 +4636,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>alive</t>
+          <t>light</t>
         </is>
       </c>
       <c r="M70" t="n">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>alive</t>
+          <t>light</t>
         </is>
       </c>
       <c r="M71" t="n">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>alive</t>
+          <t>light</t>
         </is>
       </c>
       <c r="M72" t="n">
@@ -4816,7 +4816,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>alive</t>
+          <t>light</t>
         </is>
       </c>
       <c r="M73" t="n">
@@ -7036,7 +7036,7 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>light</t>
+          <t>alive</t>
         </is>
       </c>
       <c r="M110" t="n">
@@ -7044,7 +7044,7 @@
       </c>
       <c r="N110" t="inlineStr"/>
       <c r="O110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P110" t="n">
         <v>0</v>
@@ -7096,7 +7096,7 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>light</t>
+          <t>alive</t>
         </is>
       </c>
       <c r="M111" t="n">
@@ -7224,7 +7224,7 @@
       </c>
       <c r="N113" t="inlineStr"/>
       <c r="O113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P113" t="n">
         <v>0</v>
@@ -7276,7 +7276,7 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>died_from_injury</t>
+          <t>alive</t>
         </is>
       </c>
       <c r="M114" t="n">
@@ -7456,7 +7456,7 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>alive</t>
+          <t>killed</t>
         </is>
       </c>
       <c r="M117" t="n">
@@ -7516,7 +7516,7 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>heavy</t>
+          <t>alive</t>
         </is>
       </c>
       <c r="M118" t="n">
@@ -7524,7 +7524,7 @@
       </c>
       <c r="N118" t="inlineStr"/>
       <c r="O118" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P118" t="n">
         <v>0</v>
@@ -7584,7 +7584,7 @@
       </c>
       <c r="N119" t="inlineStr"/>
       <c r="O119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P119" t="n">
         <v>0</v>
@@ -7696,7 +7696,7 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>light</t>
+          <t>alive</t>
         </is>
       </c>
       <c r="M121" t="n">
@@ -7764,7 +7764,7 @@
       </c>
       <c r="N122" t="inlineStr"/>
       <c r="O122" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P122" t="n">
         <v>0</v>
@@ -7816,7 +7816,7 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>heavy</t>
+          <t>alive</t>
         </is>
       </c>
       <c r="M123" t="n">
@@ -7884,7 +7884,7 @@
       </c>
       <c r="N124" t="inlineStr"/>
       <c r="O124" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P124" t="n">
         <v>0</v>
@@ -7996,7 +7996,7 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>alive</t>
+          <t>killed</t>
         </is>
       </c>
       <c r="M126" t="n">
@@ -8124,7 +8124,7 @@
       </c>
       <c r="N128" t="inlineStr"/>
       <c r="O128" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P128" t="n">
         <v>0</v>
@@ -8184,7 +8184,7 @@
       </c>
       <c r="N129" t="inlineStr"/>
       <c r="O129" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P129" t="n">
         <v>0</v>
@@ -8236,7 +8236,7 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>heavy</t>
+          <t>alive</t>
         </is>
       </c>
       <c r="M130" t="n">
@@ -8244,7 +8244,7 @@
       </c>
       <c r="N130" t="inlineStr"/>
       <c r="O130" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P130" t="n">
         <v>0</v>
@@ -8296,7 +8296,7 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>light</t>
+          <t>alive</t>
         </is>
       </c>
       <c r="M131" t="n">
@@ -8356,7 +8356,7 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>alive</t>
+          <t>light</t>
         </is>
       </c>
       <c r="M132" t="n">
@@ -8416,7 +8416,7 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>light</t>
+          <t>alive</t>
         </is>
       </c>
       <c r="M133" t="n">
@@ -8544,7 +8544,7 @@
       </c>
       <c r="N135" t="inlineStr"/>
       <c r="O135" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P135" t="n">
         <v>0</v>
@@ -8596,7 +8596,7 @@
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>light</t>
+          <t>alive</t>
         </is>
       </c>
       <c r="M136" t="n">
@@ -8604,7 +8604,7 @@
       </c>
       <c r="N136" t="inlineStr"/>
       <c r="O136" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P136" t="n">
         <v>0</v>
@@ -8656,7 +8656,7 @@
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>light</t>
+          <t>alive</t>
         </is>
       </c>
       <c r="M137" t="n">
@@ -8836,7 +8836,7 @@
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>alive</t>
+          <t>light</t>
         </is>
       </c>
       <c r="M140" t="n">
@@ -8844,7 +8844,7 @@
       </c>
       <c r="N140" t="inlineStr"/>
       <c r="O140" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P140" t="n">
         <v>0</v>
@@ -8896,7 +8896,7 @@
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>light</t>
+          <t>alive</t>
         </is>
       </c>
       <c r="M141" t="n">
@@ -8956,7 +8956,7 @@
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>light</t>
+          <t>alive</t>
         </is>
       </c>
       <c r="M142" t="n">
@@ -9196,7 +9196,7 @@
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>killed</t>
+          <t>alive</t>
         </is>
       </c>
       <c r="M146" t="n">
@@ -9256,7 +9256,7 @@
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>light</t>
+          <t>alive</t>
         </is>
       </c>
       <c r="M147" t="n">
@@ -9316,7 +9316,7 @@
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>light</t>
+          <t>alive</t>
         </is>
       </c>
       <c r="M148" t="n">
@@ -9384,7 +9384,7 @@
       </c>
       <c r="N149" t="inlineStr"/>
       <c r="O149" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P149" t="n">
         <v>0</v>
@@ -9496,7 +9496,7 @@
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>light</t>
+          <t>alive</t>
         </is>
       </c>
       <c r="M151" t="n">
@@ -9556,7 +9556,7 @@
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>light</t>
+          <t>alive</t>
         </is>
       </c>
       <c r="M152" t="n">
@@ -9564,7 +9564,7 @@
       </c>
       <c r="N152" t="inlineStr"/>
       <c r="O152" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P152" t="n">
         <v>0</v>
@@ -9616,7 +9616,7 @@
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>light</t>
+          <t>alive</t>
         </is>
       </c>
       <c r="M153" t="n">
@@ -9624,7 +9624,7 @@
       </c>
       <c r="N153" t="inlineStr"/>
       <c r="O153" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P153" t="n">
         <v>0</v>
@@ -9676,7 +9676,7 @@
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>alive</t>
+          <t>light</t>
         </is>
       </c>
       <c r="M154" t="n">
@@ -9684,7 +9684,7 @@
       </c>
       <c r="N154" t="inlineStr"/>
       <c r="O154" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P154" t="n">
         <v>0</v>
@@ -9796,7 +9796,7 @@
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>heavy</t>
+          <t>alive</t>
         </is>
       </c>
       <c r="M156" t="n">
@@ -9864,7 +9864,7 @@
       </c>
       <c r="N157" t="inlineStr"/>
       <c r="O157" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P157" t="n">
         <v>0</v>
@@ -9976,7 +9976,7 @@
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t>light</t>
+          <t>alive</t>
         </is>
       </c>
       <c r="M159" t="n">
@@ -10036,7 +10036,7 @@
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>heavy</t>
+          <t>alive</t>
         </is>
       </c>
       <c r="M160" t="n">
@@ -10104,7 +10104,7 @@
       </c>
       <c r="N161" t="inlineStr"/>
       <c r="O161" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P161" t="n">
         <v>0</v>
@@ -10156,7 +10156,7 @@
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t>light</t>
+          <t>alive</t>
         </is>
       </c>
       <c r="M162" t="n">
@@ -10336,7 +10336,7 @@
       </c>
       <c r="L165" t="inlineStr">
         <is>
-          <t>light</t>
+          <t>killed</t>
         </is>
       </c>
       <c r="M165" t="n">
@@ -10396,7 +10396,7 @@
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t>heavy</t>
+          <t>alive</t>
         </is>
       </c>
       <c r="M166" t="n">
@@ -10516,7 +10516,7 @@
       </c>
       <c r="L168" t="inlineStr">
         <is>
-          <t>alive</t>
+          <t>light</t>
         </is>
       </c>
       <c r="M168" t="n">
@@ -10524,7 +10524,7 @@
       </c>
       <c r="N168" t="inlineStr"/>
       <c r="O168" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P168" t="n">
         <v>0</v>
@@ -10876,7 +10876,7 @@
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t>heavy</t>
+          <t>alive</t>
         </is>
       </c>
       <c r="M174" t="n">
@@ -10936,7 +10936,7 @@
       </c>
       <c r="L175" t="inlineStr">
         <is>
-          <t>light</t>
+          <t>alive</t>
         </is>
       </c>
       <c r="M175" t="n">
@@ -10996,7 +10996,7 @@
       </c>
       <c r="L176" t="inlineStr">
         <is>
-          <t>light</t>
+          <t>alive</t>
         </is>
       </c>
       <c r="M176" t="n">
@@ -11296,7 +11296,7 @@
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t>heavy</t>
+          <t>alive</t>
         </is>
       </c>
       <c r="M181" t="n">
@@ -11356,7 +11356,7 @@
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>light</t>
+          <t>alive</t>
         </is>
       </c>
       <c r="M182" t="n">
@@ -11476,7 +11476,7 @@
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>light</t>
+          <t>alive</t>
         </is>
       </c>
       <c r="M184" t="n">
@@ -11596,7 +11596,7 @@
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>killed</t>
+          <t>alive</t>
         </is>
       </c>
       <c r="M186" t="n">
@@ -11656,7 +11656,7 @@
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>light</t>
+          <t>alive</t>
         </is>
       </c>
       <c r="M187" t="n">
@@ -11716,7 +11716,7 @@
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t>light</t>
+          <t>alive</t>
         </is>
       </c>
       <c r="M188" t="n">
@@ -11776,7 +11776,7 @@
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t>light</t>
+          <t>alive</t>
         </is>
       </c>
       <c r="M189" t="n">
@@ -11836,7 +11836,7 @@
       </c>
       <c r="L190" t="inlineStr">
         <is>
-          <t>alive</t>
+          <t>light</t>
         </is>
       </c>
       <c r="M190" t="n">
@@ -12016,7 +12016,7 @@
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>killed</t>
+          <t>alive</t>
         </is>
       </c>
       <c r="M193" t="n">
@@ -12024,7 +12024,7 @@
       </c>
       <c r="N193" t="inlineStr"/>
       <c r="O193" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P193" t="n">
         <v>0</v>
@@ -12076,7 +12076,7 @@
       </c>
       <c r="L194" t="inlineStr">
         <is>
-          <t>light</t>
+          <t>alive</t>
         </is>
       </c>
       <c r="M194" t="n">
@@ -12196,7 +12196,7 @@
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t>heavy</t>
+          <t>alive</t>
         </is>
       </c>
       <c r="M196" t="n">
@@ -12204,7 +12204,7 @@
       </c>
       <c r="N196" t="inlineStr"/>
       <c r="O196" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P196" t="n">
         <v>0</v>
@@ -12376,7 +12376,7 @@
       </c>
       <c r="L199" t="inlineStr">
         <is>
-          <t>heavy</t>
+          <t>alive</t>
         </is>
       </c>
       <c r="M199" t="n">
@@ -12384,7 +12384,7 @@
       </c>
       <c r="N199" t="inlineStr"/>
       <c r="O199" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P199" t="n">
         <v>0</v>
@@ -12436,7 +12436,7 @@
       </c>
       <c r="L200" t="inlineStr">
         <is>
-          <t>light</t>
+          <t>alive</t>
         </is>
       </c>
       <c r="M200" t="n">
@@ -12496,7 +12496,7 @@
       </c>
       <c r="L201" t="inlineStr">
         <is>
-          <t>heavy</t>
+          <t>alive</t>
         </is>
       </c>
       <c r="M201" t="n">
@@ -12676,7 +12676,7 @@
       </c>
       <c r="L204" t="inlineStr">
         <is>
-          <t>light</t>
+          <t>alive</t>
         </is>
       </c>
       <c r="M204" t="n">
@@ -12736,7 +12736,7 @@
       </c>
       <c r="L205" t="inlineStr">
         <is>
-          <t>heavy</t>
+          <t>alive</t>
         </is>
       </c>
       <c r="M205" t="n">
@@ -12796,7 +12796,7 @@
       </c>
       <c r="L206" t="inlineStr">
         <is>
-          <t>alive</t>
+          <t>light</t>
         </is>
       </c>
       <c r="M206" t="n">
@@ -12916,7 +12916,7 @@
       </c>
       <c r="L208" t="inlineStr">
         <is>
-          <t>light</t>
+          <t>alive</t>
         </is>
       </c>
       <c r="M208" t="n">
@@ -12924,7 +12924,7 @@
       </c>
       <c r="N208" t="inlineStr"/>
       <c r="O208" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P208" t="n">
         <v>0</v>
@@ -12976,7 +12976,7 @@
       </c>
       <c r="L209" t="inlineStr">
         <is>
-          <t>light</t>
+          <t>alive</t>
         </is>
       </c>
       <c r="M209" t="n">
@@ -13156,7 +13156,7 @@
       </c>
       <c r="L212" t="inlineStr">
         <is>
-          <t>heavy</t>
+          <t>alive</t>
         </is>
       </c>
       <c r="M212" t="n">
@@ -13164,7 +13164,7 @@
       </c>
       <c r="N212" t="inlineStr"/>
       <c r="O212" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P212" t="n">
         <v>0</v>
@@ -13276,7 +13276,7 @@
       </c>
       <c r="L214" t="inlineStr">
         <is>
-          <t>heavy</t>
+          <t>alive</t>
         </is>
       </c>
       <c r="M214" t="n">
@@ -13284,7 +13284,7 @@
       </c>
       <c r="N214" t="inlineStr"/>
       <c r="O214" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P214" t="n">
         <v>0</v>
@@ -13336,7 +13336,7 @@
       </c>
       <c r="L215" t="inlineStr">
         <is>
-          <t>light</t>
+          <t>alive</t>
         </is>
       </c>
       <c r="M215" t="n">
@@ -13396,7 +13396,7 @@
       </c>
       <c r="L216" t="inlineStr">
         <is>
-          <t>light</t>
+          <t>alive</t>
         </is>
       </c>
       <c r="M216" t="n">
@@ -13644,7 +13644,7 @@
       </c>
       <c r="N220" t="inlineStr"/>
       <c r="O220" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P220" t="n">
         <v>0</v>
@@ -13756,7 +13756,7 @@
       </c>
       <c r="L222" t="inlineStr">
         <is>
-          <t>light</t>
+          <t>alive</t>
         </is>
       </c>
       <c r="M222" t="n">
@@ -14004,7 +14004,7 @@
       </c>
       <c r="N226" t="inlineStr"/>
       <c r="O226" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P226" t="n">
         <v>0</v>
@@ -14176,7 +14176,7 @@
       </c>
       <c r="L229" t="inlineStr">
         <is>
-          <t>alive</t>
+          <t>light</t>
         </is>
       </c>
       <c r="M229" t="n">
@@ -14296,7 +14296,7 @@
       </c>
       <c r="L231" t="inlineStr">
         <is>
-          <t>alive</t>
+          <t>light</t>
         </is>
       </c>
       <c r="M231" t="n">
@@ -14544,7 +14544,7 @@
       </c>
       <c r="N235" t="inlineStr"/>
       <c r="O235" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P235" t="n">
         <v>0</v>
@@ -14604,7 +14604,7 @@
       </c>
       <c r="N236" t="inlineStr"/>
       <c r="O236" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P236" t="n">
         <v>0</v>
@@ -15016,7 +15016,7 @@
       </c>
       <c r="L243" t="inlineStr">
         <is>
-          <t>killed</t>
+          <t>alive</t>
         </is>
       </c>
       <c r="M243" t="n">
@@ -15024,7 +15024,7 @@
       </c>
       <c r="N243" t="inlineStr"/>
       <c r="O243" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P243" t="n">
         <v>0</v>
@@ -15144,7 +15144,7 @@
       </c>
       <c r="N245" t="inlineStr"/>
       <c r="O245" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P245" t="n">
         <v>0</v>
@@ -15196,7 +15196,7 @@
       </c>
       <c r="L246" t="inlineStr">
         <is>
-          <t>died_from_injury</t>
+          <t>alive</t>
         </is>
       </c>
       <c r="M246" t="n">
@@ -15264,7 +15264,7 @@
       </c>
       <c r="N247" t="inlineStr"/>
       <c r="O247" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P247" t="n">
         <v>0</v>
@@ -15384,7 +15384,7 @@
       </c>
       <c r="N249" t="inlineStr"/>
       <c r="O249" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P249" t="n">
         <v>0</v>
@@ -15556,7 +15556,7 @@
       </c>
       <c r="L252" t="inlineStr">
         <is>
-          <t>heavy</t>
+          <t>alive</t>
         </is>
       </c>
       <c r="M252" t="n">
@@ -15564,7 +15564,7 @@
       </c>
       <c r="N252" t="inlineStr"/>
       <c r="O252" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P252" t="n">
         <v>0</v>
@@ -15736,7 +15736,7 @@
       </c>
       <c r="L255" t="inlineStr">
         <is>
-          <t>light</t>
+          <t>alive</t>
         </is>
       </c>
       <c r="M255" t="n">
@@ -16456,7 +16456,7 @@
       </c>
       <c r="L267" t="inlineStr">
         <is>
-          <t>light</t>
+          <t>alive</t>
         </is>
       </c>
       <c r="M267" t="n">
@@ -16816,7 +16816,7 @@
       </c>
       <c r="L273" t="inlineStr">
         <is>
-          <t>light</t>
+          <t>alive</t>
         </is>
       </c>
       <c r="M273" t="n">
@@ -16996,7 +16996,7 @@
       </c>
       <c r="L276" t="inlineStr">
         <is>
-          <t>heavy</t>
+          <t>alive</t>
         </is>
       </c>
       <c r="M276" t="n">
@@ -17116,7 +17116,7 @@
       </c>
       <c r="L278" t="inlineStr">
         <is>
-          <t>heavy</t>
+          <t>alive</t>
         </is>
       </c>
       <c r="M278" t="n">
@@ -17896,7 +17896,7 @@
       </c>
       <c r="L291" t="inlineStr">
         <is>
-          <t>light</t>
+          <t>alive</t>
         </is>
       </c>
       <c r="M291" t="n">
@@ -18084,7 +18084,7 @@
       </c>
       <c r="N294" t="inlineStr"/>
       <c r="O294" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P294" t="n">
         <v>0</v>
@@ -18196,7 +18196,7 @@
       </c>
       <c r="L296" t="inlineStr">
         <is>
-          <t>light</t>
+          <t>alive</t>
         </is>
       </c>
       <c r="M296" t="n">
@@ -18204,7 +18204,7 @@
       </c>
       <c r="N296" t="inlineStr"/>
       <c r="O296" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P296" t="n">
         <v>0</v>
@@ -18256,7 +18256,7 @@
       </c>
       <c r="L297" t="inlineStr">
         <is>
-          <t>heavy</t>
+          <t>alive</t>
         </is>
       </c>
       <c r="M297" t="n">
@@ -18264,7 +18264,7 @@
       </c>
       <c r="N297" t="inlineStr"/>
       <c r="O297" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P297" t="n">
         <v>0</v>
@@ -18384,7 +18384,7 @@
       </c>
       <c r="N299" t="inlineStr"/>
       <c r="O299" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P299" t="n">
         <v>0</v>
@@ -18496,7 +18496,7 @@
       </c>
       <c r="L301" t="inlineStr">
         <is>
-          <t>heavy</t>
+          <t>alive</t>
         </is>
       </c>
       <c r="M301" t="n">
@@ -18564,7 +18564,7 @@
       </c>
       <c r="N302" t="inlineStr"/>
       <c r="O302" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P302" t="n">
         <v>0</v>
@@ -18624,7 +18624,7 @@
       </c>
       <c r="N303" t="inlineStr"/>
       <c r="O303" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P303" t="n">
         <v>0</v>
@@ -18796,7 +18796,7 @@
       </c>
       <c r="L306" t="inlineStr">
         <is>
-          <t>light</t>
+          <t>alive</t>
         </is>
       </c>
       <c r="M306" t="n">
@@ -18804,7 +18804,7 @@
       </c>
       <c r="N306" t="inlineStr"/>
       <c r="O306" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P306" t="n">
         <v>0</v>
@@ -18924,7 +18924,7 @@
       </c>
       <c r="N308" t="inlineStr"/>
       <c r="O308" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P308" t="n">
         <v>0</v>
@@ -18976,7 +18976,7 @@
       </c>
       <c r="L309" t="inlineStr">
         <is>
-          <t>died_from_injury</t>
+          <t>alive</t>
         </is>
       </c>
       <c r="M309" t="n">
@@ -19164,7 +19164,7 @@
       </c>
       <c r="N312" t="inlineStr"/>
       <c r="O312" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P312" t="n">
         <v>0</v>
@@ -19224,7 +19224,7 @@
       </c>
       <c r="N313" t="inlineStr"/>
       <c r="O313" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P313" t="n">
         <v>0</v>
@@ -19276,7 +19276,7 @@
       </c>
       <c r="L314" t="inlineStr">
         <is>
-          <t>alive</t>
+          <t>light</t>
         </is>
       </c>
       <c r="M314" t="n">
@@ -19284,7 +19284,7 @@
       </c>
       <c r="N314" t="inlineStr"/>
       <c r="O314" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P314" t="n">
         <v>0</v>
@@ -19344,7 +19344,7 @@
       </c>
       <c r="N315" t="inlineStr"/>
       <c r="O315" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P315" t="n">
         <v>0</v>
@@ -19584,7 +19584,7 @@
       </c>
       <c r="N319" t="inlineStr"/>
       <c r="O319" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P319" t="n">
         <v>0</v>
@@ -19876,7 +19876,7 @@
       </c>
       <c r="L324" t="inlineStr">
         <is>
-          <t>alive</t>
+          <t>heavy</t>
         </is>
       </c>
       <c r="M324" t="n">
@@ -19884,7 +19884,7 @@
       </c>
       <c r="N324" t="inlineStr"/>
       <c r="O324" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P324" t="n">
         <v>0</v>
@@ -19944,7 +19944,7 @@
       </c>
       <c r="N325" t="inlineStr"/>
       <c r="O325" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P325" t="n">
         <v>0</v>

--- a/player_brigade.xlsx
+++ b/player_brigade.xlsx
@@ -916,7 +916,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>alive</t>
+          <t>heavy</t>
         </is>
       </c>
       <c r="M8" t="n">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>alive</t>
+          <t>light</t>
         </is>
       </c>
       <c r="M13" t="n">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P16" t="n">
         <v>0</v>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P19" t="n">
         <v>0</v>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P20" t="n">
         <v>0</v>
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P23" t="n">
         <v>0</v>
@@ -1944,7 +1944,7 @@
       </c>
       <c r="N25" t="inlineStr"/>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P25" t="n">
         <v>0</v>
@@ -2304,7 +2304,7 @@
       </c>
       <c r="N31" t="inlineStr"/>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P31" t="n">
         <v>0</v>
@@ -2356,7 +2356,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>alive</t>
+          <t>light</t>
         </is>
       </c>
       <c r="M32" t="n">
@@ -2544,7 +2544,7 @@
       </c>
       <c r="N35" t="inlineStr"/>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P35" t="n">
         <v>0</v>
@@ -2716,7 +2716,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>heavy</t>
+          <t>alive</t>
         </is>
       </c>
       <c r="M38" t="n">
@@ -2836,7 +2836,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>light</t>
+          <t>alive</t>
         </is>
       </c>
       <c r="M40" t="n">
@@ -2896,7 +2896,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>light</t>
+          <t>alive</t>
         </is>
       </c>
       <c r="M41" t="n">
@@ -2956,7 +2956,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>light</t>
+          <t>killed</t>
         </is>
       </c>
       <c r="M42" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>light</t>
+          <t>alive</t>
         </is>
       </c>
       <c r="M44" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>light</t>
+          <t>alive</t>
         </is>
       </c>
       <c r="M50" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>light</t>
+          <t>killed</t>
         </is>
       </c>
       <c r="M51" t="n">
@@ -3616,7 +3616,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>light</t>
+          <t>alive</t>
         </is>
       </c>
       <c r="M53" t="n">
@@ -3676,7 +3676,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>alive</t>
+          <t>light</t>
         </is>
       </c>
       <c r="M54" t="n">
@@ -3684,7 +3684,7 @@
       </c>
       <c r="N54" t="inlineStr"/>
       <c r="O54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P54" t="n">
         <v>0</v>
@@ -3736,7 +3736,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>light</t>
+          <t>alive</t>
         </is>
       </c>
       <c r="M55" t="n">
@@ -3796,7 +3796,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>light</t>
+          <t>alive</t>
         </is>
       </c>
       <c r="M56" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>died_from_injury</t>
+          <t>alive</t>
         </is>
       </c>
       <c r="M57" t="n">
@@ -3984,7 +3984,7 @@
       </c>
       <c r="N59" t="inlineStr"/>
       <c r="O59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P59" t="n">
         <v>0</v>
@@ -4036,7 +4036,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>died_from_injury</t>
+          <t>alive</t>
         </is>
       </c>
       <c r="M60" t="n">
@@ -4096,7 +4096,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>light</t>
+          <t>alive</t>
         </is>
       </c>
       <c r="M61" t="n">
@@ -4156,7 +4156,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>killed</t>
+          <t>alive</t>
         </is>
       </c>
       <c r="M62" t="n">
@@ -4216,7 +4216,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>light</t>
+          <t>alive</t>
         </is>
       </c>
       <c r="M63" t="n">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>heavy</t>
+          <t>alive</t>
         </is>
       </c>
       <c r="M64" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>died_from_injury</t>
+          <t>alive</t>
         </is>
       </c>
       <c r="M65" t="n">
@@ -4396,7 +4396,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>alive</t>
+          <t>light</t>
         </is>
       </c>
       <c r="M66" t="n">
@@ -4576,7 +4576,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>light</t>
+          <t>alive</t>
         </is>
       </c>
       <c r="M69" t="n">
@@ -4636,7 +4636,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>light</t>
+          <t>alive</t>
         </is>
       </c>
       <c r="M70" t="n">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>light</t>
+          <t>alive</t>
         </is>
       </c>
       <c r="M71" t="n">
@@ -4816,7 +4816,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>light</t>
+          <t>alive</t>
         </is>
       </c>
       <c r="M73" t="n">
@@ -4884,7 +4884,7 @@
       </c>
       <c r="N74" t="inlineStr"/>
       <c r="O74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P74" t="n">
         <v>0</v>
@@ -5236,7 +5236,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>alive</t>
+          <t>light</t>
         </is>
       </c>
       <c r="M80" t="n">
@@ -5296,7 +5296,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>alive</t>
+          <t>light</t>
         </is>
       </c>
       <c r="M81" t="n">
@@ -5604,7 +5604,7 @@
       </c>
       <c r="N86" t="inlineStr"/>
       <c r="O86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P86" t="n">
         <v>0</v>
@@ -5776,7 +5776,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>alive</t>
+          <t>light</t>
         </is>
       </c>
       <c r="M89" t="n">
@@ -6144,7 +6144,7 @@
       </c>
       <c r="N95" t="inlineStr"/>
       <c r="O95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P95" t="n">
         <v>0</v>
@@ -6264,7 +6264,7 @@
       </c>
       <c r="N97" t="inlineStr"/>
       <c r="O97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P97" t="n">
         <v>0</v>
@@ -6384,7 +6384,7 @@
       </c>
       <c r="N99" t="inlineStr"/>
       <c r="O99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P99" t="n">
         <v>0</v>
@@ -6496,7 +6496,7 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>alive</t>
+          <t>light</t>
         </is>
       </c>
       <c r="M101" t="n">
@@ -6804,7 +6804,7 @@
       </c>
       <c r="N106" t="inlineStr"/>
       <c r="O106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P106" t="n">
         <v>0</v>
@@ -7044,7 +7044,7 @@
       </c>
       <c r="N110" t="inlineStr"/>
       <c r="O110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P110" t="n">
         <v>0</v>
@@ -7156,7 +7156,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>light</t>
+          <t>alive</t>
         </is>
       </c>
       <c r="M112" t="n">
@@ -7276,7 +7276,7 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>alive</t>
+          <t>light</t>
         </is>
       </c>
       <c r="M114" t="n">
@@ -7456,7 +7456,7 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>killed</t>
+          <t>light</t>
         </is>
       </c>
       <c r="M117" t="n">
@@ -7524,7 +7524,7 @@
       </c>
       <c r="N118" t="inlineStr"/>
       <c r="O118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P118" t="n">
         <v>0</v>
@@ -7584,7 +7584,7 @@
       </c>
       <c r="N119" t="inlineStr"/>
       <c r="O119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P119" t="n">
         <v>0</v>
@@ -7884,7 +7884,7 @@
       </c>
       <c r="N124" t="inlineStr"/>
       <c r="O124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P124" t="n">
         <v>0</v>
@@ -7996,7 +7996,7 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>killed</t>
+          <t>alive</t>
         </is>
       </c>
       <c r="M126" t="n">
@@ -8124,7 +8124,7 @@
       </c>
       <c r="N128" t="inlineStr"/>
       <c r="O128" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P128" t="n">
         <v>0</v>
@@ -8184,7 +8184,7 @@
       </c>
       <c r="N129" t="inlineStr"/>
       <c r="O129" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P129" t="n">
         <v>0</v>
@@ -8244,7 +8244,7 @@
       </c>
       <c r="N130" t="inlineStr"/>
       <c r="O130" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P130" t="n">
         <v>0</v>
@@ -8356,7 +8356,7 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>light</t>
+          <t>heavy</t>
         </is>
       </c>
       <c r="M132" t="n">
@@ -8424,7 +8424,7 @@
       </c>
       <c r="N133" t="inlineStr"/>
       <c r="O133" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P133" t="n">
         <v>0</v>
@@ -8596,7 +8596,7 @@
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>alive</t>
+          <t>light</t>
         </is>
       </c>
       <c r="M136" t="n">
@@ -8604,7 +8604,7 @@
       </c>
       <c r="N136" t="inlineStr"/>
       <c r="O136" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P136" t="n">
         <v>0</v>
@@ -8836,7 +8836,7 @@
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>light</t>
+          <t>alive</t>
         </is>
       </c>
       <c r="M140" t="n">
@@ -8844,7 +8844,7 @@
       </c>
       <c r="N140" t="inlineStr"/>
       <c r="O140" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P140" t="n">
         <v>0</v>
@@ -9384,7 +9384,7 @@
       </c>
       <c r="N149" t="inlineStr"/>
       <c r="O149" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P149" t="n">
         <v>0</v>
@@ -9616,7 +9616,7 @@
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>alive</t>
+          <t>light</t>
         </is>
       </c>
       <c r="M153" t="n">
@@ -9676,7 +9676,7 @@
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>light</t>
+          <t>alive</t>
         </is>
       </c>
       <c r="M154" t="n">
@@ -9736,7 +9736,7 @@
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>light</t>
+          <t>alive</t>
         </is>
       </c>
       <c r="M155" t="n">
@@ -9864,7 +9864,7 @@
       </c>
       <c r="N157" t="inlineStr"/>
       <c r="O157" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P157" t="n">
         <v>0</v>
@@ -9984,7 +9984,7 @@
       </c>
       <c r="N159" t="inlineStr"/>
       <c r="O159" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P159" t="n">
         <v>0</v>
@@ -10336,7 +10336,7 @@
       </c>
       <c r="L165" t="inlineStr">
         <is>
-          <t>killed</t>
+          <t>alive</t>
         </is>
       </c>
       <c r="M165" t="n">
@@ -10404,7 +10404,7 @@
       </c>
       <c r="N166" t="inlineStr"/>
       <c r="O166" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P166" t="n">
         <v>0</v>
@@ -10516,7 +10516,7 @@
       </c>
       <c r="L168" t="inlineStr">
         <is>
-          <t>light</t>
+          <t>alive</t>
         </is>
       </c>
       <c r="M168" t="n">
@@ -10524,7 +10524,7 @@
       </c>
       <c r="N168" t="inlineStr"/>
       <c r="O168" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P168" t="n">
         <v>0</v>
@@ -10584,7 +10584,7 @@
       </c>
       <c r="N169" t="inlineStr"/>
       <c r="O169" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P169" t="n">
         <v>0</v>
@@ -10764,7 +10764,7 @@
       </c>
       <c r="N172" t="inlineStr"/>
       <c r="O172" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P172" t="n">
         <v>0</v>
@@ -10884,7 +10884,7 @@
       </c>
       <c r="N174" t="inlineStr"/>
       <c r="O174" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P174" t="n">
         <v>0</v>
@@ -10944,7 +10944,7 @@
       </c>
       <c r="N175" t="inlineStr"/>
       <c r="O175" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P175" t="n">
         <v>0</v>
@@ -11004,7 +11004,7 @@
       </c>
       <c r="N176" t="inlineStr"/>
       <c r="O176" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P176" t="n">
         <v>0</v>
@@ -11064,7 +11064,7 @@
       </c>
       <c r="N177" t="inlineStr"/>
       <c r="O177" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P177" t="n">
         <v>0</v>
@@ -11124,7 +11124,7 @@
       </c>
       <c r="N178" t="inlineStr"/>
       <c r="O178" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P178" t="n">
         <v>0</v>
@@ -11184,7 +11184,7 @@
       </c>
       <c r="N179" t="inlineStr"/>
       <c r="O179" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P179" t="n">
         <v>0</v>
@@ -11416,7 +11416,7 @@
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>light</t>
+          <t>alive</t>
         </is>
       </c>
       <c r="M183" t="n">
@@ -11484,7 +11484,7 @@
       </c>
       <c r="N184" t="inlineStr"/>
       <c r="O184" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P184" t="n">
         <v>0</v>
@@ -11656,7 +11656,7 @@
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>alive</t>
+          <t>heavy</t>
         </is>
       </c>
       <c r="M187" t="n">
@@ -11836,7 +11836,7 @@
       </c>
       <c r="L190" t="inlineStr">
         <is>
-          <t>light</t>
+          <t>alive</t>
         </is>
       </c>
       <c r="M190" t="n">
@@ -12144,7 +12144,7 @@
       </c>
       <c r="N195" t="inlineStr"/>
       <c r="O195" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P195" t="n">
         <v>0</v>
@@ -12204,7 +12204,7 @@
       </c>
       <c r="N196" t="inlineStr"/>
       <c r="O196" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P196" t="n">
         <v>0</v>
@@ -12384,7 +12384,7 @@
       </c>
       <c r="N199" t="inlineStr"/>
       <c r="O199" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P199" t="n">
         <v>0</v>
@@ -12796,7 +12796,7 @@
       </c>
       <c r="L206" t="inlineStr">
         <is>
-          <t>light</t>
+          <t>alive</t>
         </is>
       </c>
       <c r="M206" t="n">
@@ -12924,7 +12924,7 @@
       </c>
       <c r="N208" t="inlineStr"/>
       <c r="O208" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P208" t="n">
         <v>0</v>
@@ -13164,7 +13164,7 @@
       </c>
       <c r="N212" t="inlineStr"/>
       <c r="O212" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P212" t="n">
         <v>0</v>
@@ -13284,7 +13284,7 @@
       </c>
       <c r="N214" t="inlineStr"/>
       <c r="O214" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P214" t="n">
         <v>0</v>
@@ -13336,7 +13336,7 @@
       </c>
       <c r="L215" t="inlineStr">
         <is>
-          <t>alive</t>
+          <t>killed</t>
         </is>
       </c>
       <c r="M215" t="n">
@@ -13644,7 +13644,7 @@
       </c>
       <c r="N220" t="inlineStr"/>
       <c r="O220" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P220" t="n">
         <v>0</v>
@@ -14176,7 +14176,7 @@
       </c>
       <c r="L229" t="inlineStr">
         <is>
-          <t>light</t>
+          <t>alive</t>
         </is>
       </c>
       <c r="M229" t="n">
@@ -14296,7 +14296,7 @@
       </c>
       <c r="L231" t="inlineStr">
         <is>
-          <t>light</t>
+          <t>alive</t>
         </is>
       </c>
       <c r="M231" t="n">
@@ -14356,7 +14356,7 @@
       </c>
       <c r="L232" t="inlineStr">
         <is>
-          <t>alive</t>
+          <t>light</t>
         </is>
       </c>
       <c r="M232" t="n">
@@ -14544,7 +14544,7 @@
       </c>
       <c r="N235" t="inlineStr"/>
       <c r="O235" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P235" t="n">
         <v>0</v>
@@ -14604,7 +14604,7 @@
       </c>
       <c r="N236" t="inlineStr"/>
       <c r="O236" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P236" t="n">
         <v>0</v>
@@ -15024,7 +15024,7 @@
       </c>
       <c r="N243" t="inlineStr"/>
       <c r="O243" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P243" t="n">
         <v>0</v>
@@ -15144,7 +15144,7 @@
       </c>
       <c r="N245" t="inlineStr"/>
       <c r="O245" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P245" t="n">
         <v>0</v>
@@ -15264,7 +15264,7 @@
       </c>
       <c r="N247" t="inlineStr"/>
       <c r="O247" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P247" t="n">
         <v>0</v>
@@ -15384,7 +15384,7 @@
       </c>
       <c r="N249" t="inlineStr"/>
       <c r="O249" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P249" t="n">
         <v>0</v>
@@ -15564,7 +15564,7 @@
       </c>
       <c r="N252" t="inlineStr"/>
       <c r="O252" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P252" t="n">
         <v>0</v>
@@ -15864,7 +15864,7 @@
       </c>
       <c r="N257" t="inlineStr"/>
       <c r="O257" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P257" t="n">
         <v>0</v>
@@ -16396,7 +16396,7 @@
       </c>
       <c r="L266" t="inlineStr">
         <is>
-          <t>alive</t>
+          <t>light</t>
         </is>
       </c>
       <c r="M266" t="n">
@@ -16576,7 +16576,7 @@
       </c>
       <c r="L269" t="inlineStr">
         <is>
-          <t>alive</t>
+          <t>light</t>
         </is>
       </c>
       <c r="M269" t="n">
@@ -16996,7 +16996,7 @@
       </c>
       <c r="L276" t="inlineStr">
         <is>
-          <t>alive</t>
+          <t>light</t>
         </is>
       </c>
       <c r="M276" t="n">
@@ -17056,7 +17056,7 @@
       </c>
       <c r="L277" t="inlineStr">
         <is>
-          <t>alive</t>
+          <t>light</t>
         </is>
       </c>
       <c r="M277" t="n">
@@ -17304,7 +17304,7 @@
       </c>
       <c r="N281" t="inlineStr"/>
       <c r="O281" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P281" t="n">
         <v>0</v>
@@ -17356,7 +17356,7 @@
       </c>
       <c r="L282" t="inlineStr">
         <is>
-          <t>alive</t>
+          <t>light</t>
         </is>
       </c>
       <c r="M282" t="n">
@@ -17416,7 +17416,7 @@
       </c>
       <c r="L283" t="inlineStr">
         <is>
-          <t>alive</t>
+          <t>heavy</t>
         </is>
       </c>
       <c r="M283" t="n">
@@ -17476,7 +17476,7 @@
       </c>
       <c r="L284" t="inlineStr">
         <is>
-          <t>alive</t>
+          <t>killed</t>
         </is>
       </c>
       <c r="M284" t="n">
@@ -17836,7 +17836,7 @@
       </c>
       <c r="L290" t="inlineStr">
         <is>
-          <t>alive</t>
+          <t>light</t>
         </is>
       </c>
       <c r="M290" t="n">
@@ -17956,7 +17956,7 @@
       </c>
       <c r="L292" t="inlineStr">
         <is>
-          <t>alive</t>
+          <t>light</t>
         </is>
       </c>
       <c r="M292" t="n">
@@ -18016,7 +18016,7 @@
       </c>
       <c r="L293" t="inlineStr">
         <is>
-          <t>alive</t>
+          <t>light</t>
         </is>
       </c>
       <c r="M293" t="n">
@@ -18264,7 +18264,7 @@
       </c>
       <c r="N297" t="inlineStr"/>
       <c r="O297" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P297" t="n">
         <v>0</v>
@@ -18324,7 +18324,7 @@
       </c>
       <c r="N298" t="inlineStr"/>
       <c r="O298" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P298" t="n">
         <v>0</v>
@@ -18384,7 +18384,7 @@
       </c>
       <c r="N299" t="inlineStr"/>
       <c r="O299" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P299" t="n">
         <v>0</v>
@@ -18804,7 +18804,7 @@
       </c>
       <c r="N306" t="inlineStr"/>
       <c r="O306" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P306" t="n">
         <v>0</v>
@@ -18864,7 +18864,7 @@
       </c>
       <c r="N307" t="inlineStr"/>
       <c r="O307" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P307" t="n">
         <v>0</v>
@@ -18924,7 +18924,7 @@
       </c>
       <c r="N308" t="inlineStr"/>
       <c r="O308" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P308" t="n">
         <v>0</v>
@@ -19044,7 +19044,7 @@
       </c>
       <c r="N310" t="inlineStr"/>
       <c r="O310" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P310" t="n">
         <v>0</v>
@@ -19216,7 +19216,7 @@
       </c>
       <c r="L313" t="inlineStr">
         <is>
-          <t>alive</t>
+          <t>heavy</t>
         </is>
       </c>
       <c r="M313" t="n">
@@ -19276,7 +19276,7 @@
       </c>
       <c r="L314" t="inlineStr">
         <is>
-          <t>light</t>
+          <t>alive</t>
         </is>
       </c>
       <c r="M314" t="n">
@@ -19344,7 +19344,7 @@
       </c>
       <c r="N315" t="inlineStr"/>
       <c r="O315" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P315" t="n">
         <v>0</v>
@@ -19464,7 +19464,7 @@
       </c>
       <c r="N317" t="inlineStr"/>
       <c r="O317" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P317" t="n">
         <v>0</v>
@@ -19876,7 +19876,7 @@
       </c>
       <c r="L324" t="inlineStr">
         <is>
-          <t>heavy</t>
+          <t>alive</t>
         </is>
       </c>
       <c r="M324" t="n">
@@ -19884,7 +19884,7 @@
       </c>
       <c r="N324" t="inlineStr"/>
       <c r="O324" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P324" t="n">
         <v>0</v>
@@ -19996,7 +19996,7 @@
       </c>
       <c r="L326" t="inlineStr">
         <is>
-          <t>alive</t>
+          <t>killed</t>
         </is>
       </c>
       <c r="M326" t="n">
@@ -20056,7 +20056,7 @@
       </c>
       <c r="L327" t="inlineStr">
         <is>
-          <t>alive</t>
+          <t>killed</t>
         </is>
       </c>
       <c r="M327" t="n">
@@ -20176,7 +20176,7 @@
       </c>
       <c r="L329" t="inlineStr">
         <is>
-          <t>alive</t>
+          <t>killed</t>
         </is>
       </c>
       <c r="M329" t="n">
@@ -20236,7 +20236,7 @@
       </c>
       <c r="L330" t="inlineStr">
         <is>
-          <t>alive</t>
+          <t>killed</t>
         </is>
       </c>
       <c r="M330" t="n">
@@ -20296,7 +20296,7 @@
       </c>
       <c r="L331" t="inlineStr">
         <is>
-          <t>alive</t>
+          <t>killed</t>
         </is>
       </c>
       <c r="M331" t="n">
@@ -20356,7 +20356,7 @@
       </c>
       <c r="L332" t="inlineStr">
         <is>
-          <t>alive</t>
+          <t>killed</t>
         </is>
       </c>
       <c r="M332" t="n">
@@ -20416,7 +20416,7 @@
       </c>
       <c r="L333" t="inlineStr">
         <is>
-          <t>alive</t>
+          <t>heavy</t>
         </is>
       </c>
       <c r="M333" t="n">
@@ -20476,7 +20476,7 @@
       </c>
       <c r="L334" t="inlineStr">
         <is>
-          <t>alive</t>
+          <t>killed</t>
         </is>
       </c>
       <c r="M334" t="n">
@@ -20536,7 +20536,7 @@
       </c>
       <c r="L335" t="inlineStr">
         <is>
-          <t>alive</t>
+          <t>killed</t>
         </is>
       </c>
       <c r="M335" t="n">
@@ -20716,7 +20716,7 @@
       </c>
       <c r="L338" t="inlineStr">
         <is>
-          <t>alive</t>
+          <t>killed</t>
         </is>
       </c>
       <c r="M338" t="n">
@@ -20776,7 +20776,7 @@
       </c>
       <c r="L339" t="inlineStr">
         <is>
-          <t>alive</t>
+          <t>killed</t>
         </is>
       </c>
       <c r="M339" t="n">
@@ -20896,7 +20896,7 @@
       </c>
       <c r="L341" t="inlineStr">
         <is>
-          <t>alive</t>
+          <t>killed</t>
         </is>
       </c>
       <c r="M341" t="n">
@@ -20956,7 +20956,7 @@
       </c>
       <c r="L342" t="inlineStr">
         <is>
-          <t>alive</t>
+          <t>killed</t>
         </is>
       </c>
       <c r="M342" t="n">
@@ -21016,7 +21016,7 @@
       </c>
       <c r="L343" t="inlineStr">
         <is>
-          <t>alive</t>
+          <t>killed</t>
         </is>
       </c>
       <c r="M343" t="n">
@@ -21076,7 +21076,7 @@
       </c>
       <c r="L344" t="inlineStr">
         <is>
-          <t>alive</t>
+          <t>killed</t>
         </is>
       </c>
       <c r="M344" t="n">
@@ -21136,7 +21136,7 @@
       </c>
       <c r="L345" t="inlineStr">
         <is>
-          <t>alive</t>
+          <t>killed</t>
         </is>
       </c>
       <c r="M345" t="n">
@@ -21196,7 +21196,7 @@
       </c>
       <c r="L346" t="inlineStr">
         <is>
-          <t>alive</t>
+          <t>killed</t>
         </is>
       </c>
       <c r="M346" t="n">
@@ -21256,7 +21256,7 @@
       </c>
       <c r="L347" t="inlineStr">
         <is>
-          <t>alive</t>
+          <t>killed</t>
         </is>
       </c>
       <c r="M347" t="n">
@@ -21316,7 +21316,7 @@
       </c>
       <c r="L348" t="inlineStr">
         <is>
-          <t>alive</t>
+          <t>killed</t>
         </is>
       </c>
       <c r="M348" t="n">
@@ -21376,7 +21376,7 @@
       </c>
       <c r="L349" t="inlineStr">
         <is>
-          <t>alive</t>
+          <t>killed</t>
         </is>
       </c>
       <c r="M349" t="n">
@@ -21436,7 +21436,7 @@
       </c>
       <c r="L350" t="inlineStr">
         <is>
-          <t>alive</t>
+          <t>killed</t>
         </is>
       </c>
       <c r="M350" t="n">
@@ -21496,7 +21496,7 @@
       </c>
       <c r="L351" t="inlineStr">
         <is>
-          <t>alive</t>
+          <t>killed</t>
         </is>
       </c>
       <c r="M351" t="n">
@@ -21556,7 +21556,7 @@
       </c>
       <c r="L352" t="inlineStr">
         <is>
-          <t>alive</t>
+          <t>killed</t>
         </is>
       </c>
       <c r="M352" t="n">
@@ -21616,7 +21616,7 @@
       </c>
       <c r="L353" t="inlineStr">
         <is>
-          <t>alive</t>
+          <t>killed</t>
         </is>
       </c>
       <c r="M353" t="n">
@@ -21676,7 +21676,7 @@
       </c>
       <c r="L354" t="inlineStr">
         <is>
-          <t>alive</t>
+          <t>killed</t>
         </is>
       </c>
       <c r="M354" t="n">
@@ -21736,7 +21736,7 @@
       </c>
       <c r="L355" t="inlineStr">
         <is>
-          <t>alive</t>
+          <t>killed</t>
         </is>
       </c>
       <c r="M355" t="n">
@@ -21856,7 +21856,7 @@
       </c>
       <c r="L357" t="inlineStr">
         <is>
-          <t>alive</t>
+          <t>killed</t>
         </is>
       </c>
       <c r="M357" t="n">
@@ -21916,7 +21916,7 @@
       </c>
       <c r="L358" t="inlineStr">
         <is>
-          <t>alive</t>
+          <t>killed</t>
         </is>
       </c>
       <c r="M358" t="n">
@@ -21976,7 +21976,7 @@
       </c>
       <c r="L359" t="inlineStr">
         <is>
-          <t>alive</t>
+          <t>killed</t>
         </is>
       </c>
       <c r="M359" t="n">
@@ -22036,7 +22036,7 @@
       </c>
       <c r="L360" t="inlineStr">
         <is>
-          <t>alive</t>
+          <t>killed</t>
         </is>
       </c>
       <c r="M360" t="n">
@@ -22096,7 +22096,7 @@
       </c>
       <c r="L361" t="inlineStr">
         <is>
-          <t>alive</t>
+          <t>killed</t>
         </is>
       </c>
       <c r="M361" t="n">
@@ -24436,7 +24436,7 @@
       </c>
       <c r="L400" t="inlineStr">
         <is>
-          <t>alive</t>
+          <t>killed</t>
         </is>
       </c>
       <c r="M400" t="n">
@@ -24556,7 +24556,7 @@
       </c>
       <c r="L402" t="inlineStr">
         <is>
-          <t>alive</t>
+          <t>heavy</t>
         </is>
       </c>
       <c r="M402" t="n">
@@ -24616,7 +24616,7 @@
       </c>
       <c r="L403" t="inlineStr">
         <is>
-          <t>alive</t>
+          <t>killed</t>
         </is>
       </c>
       <c r="M403" t="n">
@@ -24676,7 +24676,7 @@
       </c>
       <c r="L404" t="inlineStr">
         <is>
-          <t>alive</t>
+          <t>killed</t>
         </is>
       </c>
       <c r="M404" t="n">
@@ -24736,7 +24736,7 @@
       </c>
       <c r="L405" t="inlineStr">
         <is>
-          <t>alive</t>
+          <t>killed</t>
         </is>
       </c>
       <c r="M405" t="n">
@@ -24796,7 +24796,7 @@
       </c>
       <c r="L406" t="inlineStr">
         <is>
-          <t>alive</t>
+          <t>heavy</t>
         </is>
       </c>
       <c r="M406" t="n">
@@ -24856,7 +24856,7 @@
       </c>
       <c r="L407" t="inlineStr">
         <is>
-          <t>alive</t>
+          <t>killed</t>
         </is>
       </c>
       <c r="M407" t="n">
@@ -24916,7 +24916,7 @@
       </c>
       <c r="L408" t="inlineStr">
         <is>
-          <t>alive</t>
+          <t>killed</t>
         </is>
       </c>
       <c r="M408" t="n">
@@ -24976,7 +24976,7 @@
       </c>
       <c r="L409" t="inlineStr">
         <is>
-          <t>alive</t>
+          <t>killed</t>
         </is>
       </c>
       <c r="M409" t="n">
@@ -25036,7 +25036,7 @@
       </c>
       <c r="L410" t="inlineStr">
         <is>
-          <t>alive</t>
+          <t>killed</t>
         </is>
       </c>
       <c r="M410" t="n">
@@ -25096,7 +25096,7 @@
       </c>
       <c r="L411" t="inlineStr">
         <is>
-          <t>alive</t>
+          <t>heavy</t>
         </is>
       </c>
       <c r="M411" t="n">
@@ -25156,7 +25156,7 @@
       </c>
       <c r="L412" t="inlineStr">
         <is>
-          <t>alive</t>
+          <t>killed</t>
         </is>
       </c>
       <c r="M412" t="n">
@@ -25216,7 +25216,7 @@
       </c>
       <c r="L413" t="inlineStr">
         <is>
-          <t>alive</t>
+          <t>killed</t>
         </is>
       </c>
       <c r="M413" t="n">
@@ -25336,7 +25336,7 @@
       </c>
       <c r="L415" t="inlineStr">
         <is>
-          <t>alive</t>
+          <t>killed</t>
         </is>
       </c>
       <c r="M415" t="n">
@@ -25456,7 +25456,7 @@
       </c>
       <c r="L417" t="inlineStr">
         <is>
-          <t>alive</t>
+          <t>killed</t>
         </is>
       </c>
       <c r="M417" t="n">
@@ -25516,7 +25516,7 @@
       </c>
       <c r="L418" t="inlineStr">
         <is>
-          <t>alive</t>
+          <t>killed</t>
         </is>
       </c>
       <c r="M418" t="n">
@@ -25576,7 +25576,7 @@
       </c>
       <c r="L419" t="inlineStr">
         <is>
-          <t>alive</t>
+          <t>killed</t>
         </is>
       </c>
       <c r="M419" t="n">
@@ -25636,7 +25636,7 @@
       </c>
       <c r="L420" t="inlineStr">
         <is>
-          <t>alive</t>
+          <t>killed</t>
         </is>
       </c>
       <c r="M420" t="n">
@@ -25696,7 +25696,7 @@
       </c>
       <c r="L421" t="inlineStr">
         <is>
-          <t>alive</t>
+          <t>light</t>
         </is>
       </c>
       <c r="M421" t="n">
@@ -25756,7 +25756,7 @@
       </c>
       <c r="L422" t="inlineStr">
         <is>
-          <t>alive</t>
+          <t>killed</t>
         </is>
       </c>
       <c r="M422" t="n">
@@ -25816,7 +25816,7 @@
       </c>
       <c r="L423" t="inlineStr">
         <is>
-          <t>alive</t>
+          <t>killed</t>
         </is>
       </c>
       <c r="M423" t="n">
@@ -25876,7 +25876,7 @@
       </c>
       <c r="L424" t="inlineStr">
         <is>
-          <t>alive</t>
+          <t>killed</t>
         </is>
       </c>
       <c r="M424" t="n">
@@ -25936,7 +25936,7 @@
       </c>
       <c r="L425" t="inlineStr">
         <is>
-          <t>alive</t>
+          <t>killed</t>
         </is>
       </c>
       <c r="M425" t="n">
@@ -25996,7 +25996,7 @@
       </c>
       <c r="L426" t="inlineStr">
         <is>
-          <t>alive</t>
+          <t>killed</t>
         </is>
       </c>
       <c r="M426" t="n">
@@ -26056,7 +26056,7 @@
       </c>
       <c r="L427" t="inlineStr">
         <is>
-          <t>alive</t>
+          <t>killed</t>
         </is>
       </c>
       <c r="M427" t="n">
@@ -26116,7 +26116,7 @@
       </c>
       <c r="L428" t="inlineStr">
         <is>
-          <t>alive</t>
+          <t>killed</t>
         </is>
       </c>
       <c r="M428" t="n">
@@ -26176,7 +26176,7 @@
       </c>
       <c r="L429" t="inlineStr">
         <is>
-          <t>alive</t>
+          <t>killed</t>
         </is>
       </c>
       <c r="M429" t="n">
@@ -26296,7 +26296,7 @@
       </c>
       <c r="L431" t="inlineStr">
         <is>
-          <t>alive</t>
+          <t>killed</t>
         </is>
       </c>
       <c r="M431" t="n">
@@ -26356,7 +26356,7 @@
       </c>
       <c r="L432" t="inlineStr">
         <is>
-          <t>alive</t>
+          <t>killed</t>
         </is>
       </c>
       <c r="M432" t="n">
